--- a/excelReport/spell-check-report.xlsx
+++ b/excelReport/spell-check-report.xlsx
@@ -453,7 +453,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>https://www.softwebsolutions.com/quality-inspect</v>
+        <v>https://www.softwebsolutions.com/quality-inspect/</v>
       </c>
       <c r="B4" t="str">
         <v/>
